--- a/results_new.xlsx
+++ b/results_new.xlsx
@@ -36,12 +36,17 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00efbdbd"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -61,11 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -649,152 +655,152 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>19.08.2025</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>763250</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>GE ASSIST, ADWS, POG-DIRECTD</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>PMS-COLLCTS-OTER JURISDICT.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>GENERALI FND</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>11771.34</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>20.08.2025</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>721310</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>PERSONAS SERVICED</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>TERMINL LEAV</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>GENERALS FND</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>98209.92</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>21.08.2025</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>722210</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>PERSONAR SERVICEE</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>UNEMPLOIMENT COMEN.-PAWROLL</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>GENARAL FDUN</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>54.27</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>91</v>
       </c>
     </row>
@@ -12699,52 +12705,52 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="inlineStr">
+      <c r="A246" s="4" t="inlineStr">
         <is>
           <t>callcenter</t>
         </is>
       </c>
-      <c r="B246" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C246" s="3" t="inlineStr">
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
         <is>
           <t>515600</t>
         </is>
       </c>
-      <c r="D246" s="3" t="inlineStr">
+      <c r="D246" s="4" t="inlineStr">
         <is>
           <t>PERSONAL SERVICES</t>
         </is>
       </c>
-      <c r="E246" s="3" t="inlineStr">
+      <c r="E246" s="4" t="inlineStr">
         <is>
           <t>TELEPHONE CALL CENTERS</t>
         </is>
       </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>GENERAL FUND</t>
-        </is>
-      </c>
-      <c r="G246" s="3" t="inlineStr">
+      <c r="F246" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL FUND</t>
+        </is>
+      </c>
+      <c r="G246" s="4" t="inlineStr">
         <is>
           <t>935098.56</t>
         </is>
       </c>
-      <c r="H246" s="3" t="inlineStr">
+      <c r="H246" s="4" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="I246" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J246" s="3" t="n">
+      <c r="I246" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J246" s="4" t="n">
         <v>96</v>
       </c>
     </row>
@@ -16999,52 +17005,52 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B332" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C332" s="3" t="inlineStr">
+      <c r="A332" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B332" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
         <is>
           <t>533230</t>
         </is>
       </c>
-      <c r="D332" s="3" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVE EXPENSE</t>
-        </is>
-      </c>
-      <c r="E332" s="3" t="inlineStr">
+      <c r="D332" s="4" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE EXPENSE</t>
+        </is>
+      </c>
+      <c r="E332" s="4" t="inlineStr">
         <is>
           <t>MTCE-REP.-TELE.EQUIP. IN-HOUSE</t>
         </is>
       </c>
-      <c r="F332" s="3" t="inlineStr">
-        <is>
-          <t>GENERAL FUND</t>
-        </is>
-      </c>
-      <c r="G332" s="3" t="inlineStr">
+      <c r="F332" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL FUND</t>
+        </is>
+      </c>
+      <c r="G332" s="4" t="inlineStr">
         <is>
           <t>469.43</t>
         </is>
       </c>
-      <c r="H332" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I332" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J332" s="3" t="n">
+      <c r="H332" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I332" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J332" s="4" t="n">
         <v>91</v>
       </c>
     </row>
@@ -18049,52 +18055,52 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B353" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C353" s="3" t="inlineStr">
+      <c r="A353" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B353" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr">
         <is>
           <t>533230</t>
         </is>
       </c>
-      <c r="D353" s="3" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVE EXPENSE</t>
-        </is>
-      </c>
-      <c r="E353" s="3" t="inlineStr">
+      <c r="D353" s="4" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE EXPENSE</t>
+        </is>
+      </c>
+      <c r="E353" s="4" t="inlineStr">
         <is>
           <t>MTCE-REP.-TELE.EQUIP. IN-HOUSE</t>
         </is>
       </c>
-      <c r="F353" s="3" t="inlineStr">
-        <is>
-          <t>GENERAL FUND</t>
-        </is>
-      </c>
-      <c r="G353" s="3" t="inlineStr">
+      <c r="F353" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL FUND</t>
+        </is>
+      </c>
+      <c r="G353" s="4" t="inlineStr">
         <is>
           <t>11218.83</t>
         </is>
       </c>
-      <c r="H353" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I353" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J353" s="3" t="n">
+      <c r="H353" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I353" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J353" s="4" t="n">
         <v>91</v>
       </c>
     </row>
@@ -19699,52 +19705,52 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B386" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C386" s="3" t="inlineStr">
+      <c r="A386" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B386" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C386" s="4" t="inlineStr">
         <is>
           <t>533230</t>
         </is>
       </c>
-      <c r="D386" s="3" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVE EXPENSE</t>
-        </is>
-      </c>
-      <c r="E386" s="3" t="inlineStr">
+      <c r="D386" s="4" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE EXPENSE</t>
+        </is>
+      </c>
+      <c r="E386" s="4" t="inlineStr">
         <is>
           <t>MTCE-REP.-TELE.EQUIP. IN-HOUSE</t>
         </is>
       </c>
-      <c r="F386" s="3" t="inlineStr">
-        <is>
-          <t>GENERAL FUND</t>
-        </is>
-      </c>
-      <c r="G386" s="3" t="inlineStr">
+      <c r="F386" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL FUND</t>
+        </is>
+      </c>
+      <c r="G386" s="4" t="inlineStr">
         <is>
           <t>373.63</t>
         </is>
       </c>
-      <c r="H386" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I386" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J386" s="3" t="n">
+      <c r="H386" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I386" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J386" s="4" t="n">
         <v>91</v>
       </c>
     </row>
@@ -24649,52 +24655,52 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="3" t="inlineStr">
+      <c r="A485" s="4" t="inlineStr">
         <is>
           <t>callcenter</t>
         </is>
       </c>
-      <c r="B485" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C485" s="3" t="inlineStr">
+      <c r="B485" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C485" s="4" t="inlineStr">
         <is>
           <t>515600</t>
         </is>
       </c>
-      <c r="D485" s="3" t="inlineStr">
+      <c r="D485" s="4" t="inlineStr">
         <is>
           <t>PERSONAL SERVICES</t>
         </is>
       </c>
-      <c r="E485" s="3" t="inlineStr">
+      <c r="E485" s="4" t="inlineStr">
         <is>
           <t>TELEPHONE CALL CENTERS</t>
         </is>
       </c>
-      <c r="F485" s="3" t="inlineStr">
-        <is>
-          <t>GENERAL FUND</t>
-        </is>
-      </c>
-      <c r="G485" s="3" t="inlineStr">
+      <c r="F485" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL FUND</t>
+        </is>
+      </c>
+      <c r="G485" s="4" t="inlineStr">
         <is>
           <t>919641.47</t>
         </is>
       </c>
-      <c r="H485" s="3" t="inlineStr">
+      <c r="H485" s="4" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="I485" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J485" s="3" t="n">
+      <c r="I485" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J485" s="4" t="n">
         <v>96</v>
       </c>
     </row>
@@ -42999,52 +43005,52 @@
       </c>
     </row>
     <row r="852">
-      <c r="A852" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B852" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C852" s="3" t="inlineStr">
+      <c r="A852" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B852" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C852" s="4" t="inlineStr">
         <is>
           <t>533230</t>
         </is>
       </c>
-      <c r="D852" s="3" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVE EXPENSE</t>
-        </is>
-      </c>
-      <c r="E852" s="3" t="inlineStr">
+      <c r="D852" s="4" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE EXPENSE</t>
+        </is>
+      </c>
+      <c r="E852" s="4" t="inlineStr">
         <is>
           <t>MTCE-REP.-TELE.EQUIP. IN-HOUSE</t>
         </is>
       </c>
-      <c r="F852" s="3" t="inlineStr">
+      <c r="F852" s="4" t="inlineStr">
         <is>
           <t>HIGHER EDUCATION COMPONENT UNITS</t>
         </is>
       </c>
-      <c r="G852" s="3" t="inlineStr">
+      <c r="G852" s="4" t="inlineStr">
         <is>
           <t>2173</t>
         </is>
       </c>
-      <c r="H852" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I852" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J852" s="3" t="n">
+      <c r="H852" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I852" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J852" s="4" t="n">
         <v>91</v>
       </c>
     </row>
@@ -47799,52 +47805,52 @@
       </c>
     </row>
     <row r="948">
-      <c r="A948" s="3" t="inlineStr">
+      <c r="A948" s="4" t="inlineStr">
         <is>
           <t>callcenter</t>
         </is>
       </c>
-      <c r="B948" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C948" s="3" t="inlineStr">
+      <c r="B948" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C948" s="4" t="inlineStr">
         <is>
           <t>515600</t>
         </is>
       </c>
-      <c r="D948" s="3" t="inlineStr">
+      <c r="D948" s="4" t="inlineStr">
         <is>
           <t>PERSONAL SERVICES</t>
         </is>
       </c>
-      <c r="E948" s="3" t="inlineStr">
+      <c r="E948" s="4" t="inlineStr">
         <is>
           <t>TELEPHONE CALL CENTERS</t>
         </is>
       </c>
-      <c r="F948" s="3" t="inlineStr">
+      <c r="F948" s="4" t="inlineStr">
         <is>
           <t>HIGHER EDUCATION COMPONENT UNITS</t>
         </is>
       </c>
-      <c r="G948" s="3" t="inlineStr">
+      <c r="G948" s="4" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="H948" s="3" t="inlineStr">
+      <c r="H948" s="4" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="I948" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J948" s="3" t="n">
+      <c r="I948" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J948" s="4" t="n">
         <v>96</v>
       </c>
     </row>
@@ -49249,52 +49255,52 @@
       </c>
     </row>
     <row r="977">
-      <c r="A977" s="3" t="inlineStr">
+      <c r="A977" s="4" t="inlineStr">
         <is>
           <t>callcenter</t>
         </is>
       </c>
-      <c r="B977" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C977" s="3" t="inlineStr">
+      <c r="B977" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C977" s="4" t="inlineStr">
         <is>
           <t>515600</t>
         </is>
       </c>
-      <c r="D977" s="3" t="inlineStr">
+      <c r="D977" s="4" t="inlineStr">
         <is>
           <t>PERSONAL SERVICES</t>
         </is>
       </c>
-      <c r="E977" s="3" t="inlineStr">
+      <c r="E977" s="4" t="inlineStr">
         <is>
           <t>TELEPHONE CALL CENTERS</t>
         </is>
       </c>
-      <c r="F977" s="3" t="inlineStr">
+      <c r="F977" s="4" t="inlineStr">
         <is>
           <t>HIGHER EDUCATION COMPONENT UNITS</t>
         </is>
       </c>
-      <c r="G977" s="3" t="inlineStr">
+      <c r="G977" s="4" t="inlineStr">
         <is>
           <t>225</t>
         </is>
       </c>
-      <c r="H977" s="3" t="inlineStr">
+      <c r="H977" s="4" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="I977" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J977" s="3" t="n">
+      <c r="I977" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J977" s="4" t="n">
         <v>96</v>
       </c>
     </row>
@@ -65399,52 +65405,52 @@
       </c>
     </row>
     <row r="1300">
-      <c r="A1300" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B1300" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C1300" s="3" t="inlineStr">
+      <c r="A1300" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B1300" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C1300" s="4" t="inlineStr">
         <is>
           <t>533230</t>
         </is>
       </c>
-      <c r="D1300" s="3" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVE EXPENSE</t>
-        </is>
-      </c>
-      <c r="E1300" s="3" t="inlineStr">
+      <c r="D1300" s="4" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE EXPENSE</t>
+        </is>
+      </c>
+      <c r="E1300" s="4" t="inlineStr">
         <is>
           <t>MTCE-REP.-TELE.EQUIP. IN-HOUSE</t>
         </is>
       </c>
-      <c r="F1300" s="3" t="inlineStr">
+      <c r="F1300" s="4" t="inlineStr">
         <is>
           <t>HIGHER EDUCATION COMPONENT UNITS</t>
         </is>
       </c>
-      <c r="G1300" s="3" t="inlineStr">
+      <c r="G1300" s="4" t="inlineStr">
         <is>
           <t>312</t>
         </is>
       </c>
-      <c r="H1300" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I1300" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J1300" s="3" t="n">
+      <c r="H1300" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I1300" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J1300" s="4" t="n">
         <v>91</v>
       </c>
     </row>
@@ -66849,52 +66855,52 @@
       </c>
     </row>
     <row r="1329">
-      <c r="A1329" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B1329" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C1329" s="3" t="inlineStr">
+      <c r="A1329" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B1329" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C1329" s="4" t="inlineStr">
         <is>
           <t>533230</t>
         </is>
       </c>
-      <c r="D1329" s="3" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVE EXPENSE</t>
-        </is>
-      </c>
-      <c r="E1329" s="3" t="inlineStr">
+      <c r="D1329" s="4" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE EXPENSE</t>
+        </is>
+      </c>
+      <c r="E1329" s="4" t="inlineStr">
         <is>
           <t>MTCE-REP.-TELE.EQUIP. IN-HOUSE</t>
         </is>
       </c>
-      <c r="F1329" s="3" t="inlineStr">
+      <c r="F1329" s="4" t="inlineStr">
         <is>
           <t>HIGHER EDUCATION COMPONENT UNITS</t>
         </is>
       </c>
-      <c r="G1329" s="3" t="inlineStr">
+      <c r="G1329" s="4" t="inlineStr">
         <is>
           <t>1025.76</t>
         </is>
       </c>
-      <c r="H1329" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I1329" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J1329" s="3" t="n">
+      <c r="H1329" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I1329" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J1329" s="4" t="n">
         <v>91</v>
       </c>
     </row>
@@ -67749,52 +67755,52 @@
       </c>
     </row>
     <row r="1347">
-      <c r="A1347" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="B1347" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C1347" s="3" t="inlineStr">
+      <c r="A1347" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B1347" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C1347" s="4" t="inlineStr">
         <is>
           <t>533230</t>
         </is>
       </c>
-      <c r="D1347" s="3" t="inlineStr">
-        <is>
-          <t>ADMINISTRATIVE EXPENSE</t>
-        </is>
-      </c>
-      <c r="E1347" s="3" t="inlineStr">
+      <c r="D1347" s="4" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVE EXPENSE</t>
+        </is>
+      </c>
+      <c r="E1347" s="4" t="inlineStr">
         <is>
           <t>MTCE-REP.-TELE.EQUIP. IN-HOUSE</t>
         </is>
       </c>
-      <c r="F1347" s="3" t="inlineStr">
+      <c r="F1347" s="4" t="inlineStr">
         <is>
           <t>HIGHER EDUCATION COMPONENT UNITS</t>
         </is>
       </c>
-      <c r="G1347" s="3" t="inlineStr">
+      <c r="G1347" s="4" t="inlineStr">
         <is>
           <t>5261</t>
         </is>
       </c>
-      <c r="H1347" s="3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I1347" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J1347" s="3" t="n">
+      <c r="H1347" s="4" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I1347" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J1347" s="4" t="n">
         <v>91</v>
       </c>
     </row>
@@ -69349,52 +69355,52 @@
       </c>
     </row>
     <row r="1379">
-      <c r="A1379" s="3" t="inlineStr">
+      <c r="A1379" s="4" t="inlineStr">
         <is>
           <t>callcenter</t>
         </is>
       </c>
-      <c r="B1379" s="3" t="inlineStr">
-        <is>
-          <t>01.02.2021</t>
-        </is>
-      </c>
-      <c r="C1379" s="3" t="inlineStr">
+      <c r="B1379" s="4" t="inlineStr">
+        <is>
+          <t>01.02.2021</t>
+        </is>
+      </c>
+      <c r="C1379" s="4" t="inlineStr">
         <is>
           <t>515600</t>
         </is>
       </c>
-      <c r="D1379" s="3" t="inlineStr">
+      <c r="D1379" s="4" t="inlineStr">
         <is>
           <t>PERSONAL SERVICES</t>
         </is>
       </c>
-      <c r="E1379" s="3" t="inlineStr">
+      <c r="E1379" s="4" t="inlineStr">
         <is>
           <t>TELEPHONE CALL CENTERS</t>
         </is>
       </c>
-      <c r="F1379" s="3" t="inlineStr">
+      <c r="F1379" s="4" t="inlineStr">
         <is>
           <t>HIGHER EDUCATION COMPONENT UNITS</t>
         </is>
       </c>
-      <c r="G1379" s="3" t="inlineStr">
+      <c r="G1379" s="4" t="inlineStr">
         <is>
           <t>52.45</t>
         </is>
       </c>
-      <c r="H1379" s="3" t="inlineStr">
+      <c r="H1379" s="4" t="inlineStr">
         <is>
           <t>support</t>
         </is>
       </c>
-      <c r="I1379" s="3" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="J1379" s="3" t="n">
+      <c r="I1379" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J1379" s="4" t="n">
         <v>96</v>
       </c>
     </row>
